--- a/output/full_scan/batch_seq5_2026-07-16.xlsx
+++ b/output/full_scan/batch_seq5_2026-07-16.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O238"/>
+  <dimension ref="A1:O239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4989</v>
+        <v>4542</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>416.7929455642432</v>
+        <v>419.3645807790803</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>78.2</v>
+        <v>363.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.39062587387469</v>
+        <v>48.76598207287002</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.85156902901422</v>
+        <v>31.31699988497066</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3310168485197295</v>
+        <v>0.1345559965214035</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.906431827254956</v>
+        <v>-14.71598891261599</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>4938</v>
+        <v>4989</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>413.8818923255094</v>
+        <v>416.7929455642432</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>83.2</v>
+        <v>78.2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.68633628874559</v>
+        <v>39.39062587387469</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>10.63262038847742</v>
+        <v>17.85156902901422</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5854664055275848</v>
+        <v>0.3310168485197295</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0203324705006094</v>
+        <v>-1.906431827254956</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6155</v>
+        <v>4938</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>411.435734755283</v>
+        <v>413.8818923255094</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>66.8</v>
+        <v>83.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.33106596225095</v>
+        <v>47.68633628874559</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>30.34212192349354</v>
+        <v>10.63262038847742</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3448115322711744</v>
+        <v>0.5854664055275848</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.247814914551568</v>
+        <v>-0.0203324705006094</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>4195</v>
+        <v>6155</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>基米-創</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>411.3121964438256</v>
+        <v>411.435734755283</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16.9</v>
+        <v>66.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.99950898265252</v>
+        <v>38.33106596225095</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>29.29906760639724</v>
+        <v>30.34212192349354</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5109377020330507</v>
+        <v>0.3448115322711744</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2536461499975238</v>
+        <v>-3.247814914551568</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>5283</v>
+        <v>4195</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>禾聯碩</t>
+          <t>基米-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>408.0443868062866</v>
+        <v>411.3121964438256</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>53.4</v>
+        <v>16.9</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.25171858379466</v>
+        <v>47.99950898265252</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.22117049293853</v>
+        <v>29.29906760639724</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5017993730331649</v>
+        <v>0.5109377020330507</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>2</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.07262096651083109</v>
+        <v>0.2536461499975238</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>5906</v>
+        <v>5283</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>台南-KY</t>
+          <t>禾聯碩</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>405.8396419606401</v>
+        <v>408.0443868062866</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>37.95</v>
+        <v>53.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.18136427383848</v>
+        <v>49.25171858379466</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6.022598403555543</v>
+        <v>16.22117049293853</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.0349738395680031</v>
+        <v>0.5017993730331649</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.8908695955117654</v>
+        <v>-0.07262096651083109</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>4414</v>
+        <v>5906</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>如興</t>
+          <t>台南-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>405.767291229731</v>
+        <v>405.8396419606401</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>8.6</v>
+        <v>37.95</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>48.38431973435357</v>
+        <v>52.18136427383848</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>20.60372803450745</v>
+        <v>6.022598403555543</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4415325106192372</v>
+        <v>0.0349738395680031</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0002696053262092</v>
+        <v>0.8908695955117654</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6129</v>
+        <v>4414</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>普誠</t>
+          <t>如興</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>404.2011295948183</v>
+        <v>405.767291229731</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>16.65</v>
+        <v>8.6</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.94705980065727</v>
+        <v>48.38431973435357</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>27.2526433318023</v>
+        <v>20.60372803450745</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3269168486126323</v>
+        <v>0.4415325106192372</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3120972501288984</v>
+        <v>0.0002696053262092</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>5469</v>
+        <v>6129</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>普誠</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>403.5988422139668</v>
+        <v>404.2011295948183</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>73.2</v>
+        <v>16.65</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>31.33427804759805</v>
+        <v>43.94705980065727</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.90779415045402</v>
+        <v>27.2526433318023</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5718446995006935</v>
+        <v>0.3269168486126323</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.53878726325342</v>
+        <v>-0.3120972501288984</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>凱鈺</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>401.3772436739876</v>
+        <v>403.5988422139668</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>25.75</v>
+        <v>73.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.42811452110926</v>
+        <v>31.33427804759805</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.65365886035709</v>
+        <v>20.90779415045402</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.245592886442335</v>
+        <v>0.5718446995006935</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.164905058758657</v>
+        <v>-1.53878726325342</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>5392</v>
+        <v>5468</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>凱鈺</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>396.5240640202224</v>
+        <v>401.3772436739876</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>44.55</v>
+        <v>25.75</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.56713711340054</v>
+        <v>45.42811452110926</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.73205465880314</v>
+        <v>24.65365886035709</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.1780373630057621</v>
+        <v>0.245592886442335</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.3459693992151821</v>
+        <v>-1.164905058758657</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>5353</v>
+        <v>5392</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>396.5076529745784</v>
+        <v>396.5240640202224</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>28.6</v>
+        <v>44.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.49868898564949</v>
+        <v>47.56713711340054</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>34.41674757650807</v>
+        <v>12.73205465880314</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3975717884359228</v>
+        <v>0.1780373630057621</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.488375282086733</v>
+        <v>-0.3459693992151821</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>5228</v>
+        <v>5353</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>395.2358418391492</v>
+        <v>396.5076529745784</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>48.35</v>
+        <v>28.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>33.54386388181648</v>
+        <v>38.49868898564949</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.58385315556692</v>
+        <v>34.41674757650807</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3727076918547735</v>
+        <v>0.3975717884359228</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-2.498314013703697</v>
+        <v>-0.488375282086733</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>5230</v>
+        <v>5228</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>393.834660658499</v>
+        <v>395.2358418391492</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>19.3</v>
+        <v>48.35</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.48606575408216</v>
+        <v>33.54386388181648</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>25.86060264376633</v>
+        <v>27.58385315556692</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1698734848680161</v>
+        <v>0.3727076918547735</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.3302745190973468</v>
+        <v>-2.498314013703697</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6005</v>
+        <v>5230</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>393.6741019941434</v>
+        <v>393.834660658499</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>34.65</v>
+        <v>19.3</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.59660690923467</v>
+        <v>46.48606575408216</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>25.32260734235289</v>
+        <v>25.86060264376633</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3237516654840646</v>
+        <v>0.1698734848680161</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.6048284699012032</v>
+        <v>-0.3302745190973468</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>4991</v>
+        <v>6005</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>393.4792231880111</v>
+        <v>393.6741019941434</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>400</v>
+        <v>34.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>33.28625166545538</v>
+        <v>38.59660690923467</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>33.945784010804</v>
+        <v>25.32260734235289</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9866341460603923</v>
+        <v>0.3237516654840646</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-8.167601453913832</v>
+        <v>-0.6048284699012032</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>4979</v>
+        <v>4991</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>392.52034738394</v>
+        <v>393.4792231880111</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>32.94192224872685</v>
+        <v>33.28625166545538</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.6207405178331</v>
+        <v>33.945784010804</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7629239987806691</v>
+        <v>0.9866341460603923</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-3.660246561607714</v>
+        <v>-8.167601453913832</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>4908</v>
+        <v>4979</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>391.2298432839845</v>
+        <v>392.52034738394</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>151.5</v>
+        <v>392</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.46208702305881</v>
+        <v>32.94192224872685</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.75321956426394</v>
+        <v>18.6207405178331</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4107761771782153</v>
+        <v>0.7629239987806691</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-1.99199554159368</v>
+        <v>-3.660246561607714</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>4545</v>
+        <v>4908</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>388.0426327534912</v>
+        <v>391.2298432839845</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>35.15</v>
+        <v>151.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.0649997510617</v>
+        <v>34.46208702305881</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>26.2047016053462</v>
+        <v>19.75321956426394</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3366985848404444</v>
+        <v>0.4107761771782153</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.4700032100611495</v>
+        <v>-1.99199554159368</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>4915</v>
+        <v>4545</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>386.4876243601569</v>
+        <v>388.0426327534912</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>35.15</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.12086124996011</v>
+        <v>43.0649997510617</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>22.51449532826588</v>
+        <v>26.2047016053462</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4281084175424181</v>
+        <v>0.3366985848404444</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.09676918611602441</v>
+        <v>-0.4700032100611495</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>4995</v>
+        <v>4915</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>晶達</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>385.4705112207369</v>
+        <v>386.4876243601569</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>46</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>54.65967268597262</v>
+        <v>37.12086124996011</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.04300524047648</v>
+        <v>22.51449532826588</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7361138006290856</v>
+        <v>0.4281084175424181</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0977854228639238</v>
+        <v>-0.09676918611602441</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6163</v>
+        <v>4995</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>晶達</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>376.4482216683818</v>
+        <v>385.4705112207369</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>44.55</v>
+        <v>46</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>34.62885645087036</v>
+        <v>54.65967268597262</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>31.3332032081625</v>
+        <v>17.04300524047648</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4466313401621983</v>
+        <v>0.7361138006290856</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2325576402640088</v>
+        <v>0.0977854228639238</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>4190</v>
+        <v>6163</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>佐登-KY</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>375.5123073522881</v>
+        <v>376.4482216683818</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>25.65</v>
+        <v>44.55</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>54.77497277200739</v>
+        <v>34.62885645087036</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>37.06873179669385</v>
+        <v>31.3332032081625</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3429394904661896</v>
+        <v>0.4466313401621983</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0705363576085461</v>
+        <v>-0.2325576402640088</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>5234</v>
+        <v>4190</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>佐登-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>374.5922015098822</v>
+        <v>375.5123073522881</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>364</v>
+        <v>25.65</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>39.2205180789676</v>
+        <v>54.77497277200739</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20.16933038127796</v>
+        <v>37.06873179669385</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7605851931301139</v>
+        <v>0.3429394904661896</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-2.106431011974232</v>
+        <v>0.0705363576085461</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4760</v>
+        <v>5234</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>374.0550769534057</v>
+        <v>374.5922015098822</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>275.5</v>
+        <v>364</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>35.42570695167461</v>
+        <v>39.2205180789676</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>21.74416229963482</v>
+        <v>20.16933038127796</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3798804719951476</v>
+        <v>0.7605851931301139</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-7.269396535371634</v>
+        <v>-2.106431011974232</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>5284</v>
+        <v>4760</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>jpp-KY</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>373.0661652146986</v>
+        <v>374.0550769534057</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>299.5</v>
+        <v>275.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>29.08092252963392</v>
+        <v>35.42570695167461</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>22.92434851124379</v>
+        <v>21.74416229963482</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.8118193414280782</v>
+        <v>0.3798804719951476</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-7.973364765295326</v>
+        <v>-7.269396535371634</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>4739</v>
+        <v>5284</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>康普</t>
+          <t>jpp-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>372.4052338320656</v>
+        <v>373.0661652146986</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>299.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>34.09309680604008</v>
+        <v>29.08092252963392</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>23.37908454036012</v>
+        <v>22.92434851124379</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3046309451979183</v>
+        <v>0.8118193414280782</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-3.145699708384026</v>
+        <v>-7.973364765295326</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4942</v>
+        <v>4739</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>康普</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>371.2230109570194</v>
+        <v>372.4052338320656</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>37.6</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.96077430066364</v>
+        <v>34.09309680604008</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.61772886412555</v>
+        <v>23.37908454036012</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4321731361168125</v>
+        <v>0.3046309451979183</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.000194206345082</v>
+        <v>-3.145699708384026</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>4904</v>
+        <v>4942</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>370.7844420702906</v>
+        <v>371.2230109570194</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>101</v>
+        <v>37.6</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.48726114726912</v>
+        <v>49.96077430066364</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>25.61606143870012</v>
+        <v>11.61772886412555</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.701329030109653</v>
+        <v>0.4321731361168125</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.9657044557252414</v>
+        <v>0.000194206345082</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5484</v>
+        <v>4904</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>370.1446125459897</v>
+        <v>370.7844420702906</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>46.55</v>
+        <v>101</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>48.31040339360521</v>
+        <v>49.48726114726912</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>22.07155583320039</v>
+        <v>25.61606143870012</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3946422675035335</v>
+        <v>0.701329030109653</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0135134874041771</v>
+        <v>-0.9657044557252414</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4577</v>
+        <v>5484</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>368.9503438994728</v>
+        <v>370.1446125459897</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>46.55</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>32.57145466158121</v>
+        <v>48.31040339360521</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>21.9696603895756</v>
+        <v>22.07155583320039</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4287449014330478</v>
+        <v>0.3946422675035335</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.3655956253098411</v>
+        <v>0.0135134874041771</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>5289</v>
+        <v>4577</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>368.5594720219069</v>
+        <v>368.9503438994728</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>1395</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>35.44091324723752</v>
+        <v>32.57145466158121</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>24.80386599139617</v>
+        <v>21.9696603895756</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7730385511970335</v>
+        <v>0.4287449014330478</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>1</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-31.42712865469811</v>
+        <v>-0.3655956253098411</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>4924</v>
+        <v>5289</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>366.9175160047796</v>
+        <v>368.5594720219069</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10.25</v>
+        <v>1395</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>35.01225701839516</v>
+        <v>35.44091324723752</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>27.48858026565096</v>
+        <v>24.80386599139617</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.421072486493689</v>
+        <v>0.7730385511970335</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.4388052574035063</v>
+        <v>-31.42712865469811</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5475</v>
+        <v>4924</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>366.4281538605649</v>
+        <v>366.9175160047796</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>175.5</v>
+        <v>10.25</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,49 +7230,49 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>30.5327289957459</v>
+        <v>35.01225701839516</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>27.21716625470212</v>
+        <v>27.48858026565096</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6756847864898822</v>
+        <v>0.421072486493689</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-4.793313210568286</v>
+        <v>-0.4388052574035063</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>5607</v>
+        <v>5475</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>遠雄港</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>365.9508617738881</v>
+        <v>366.4281538605649</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>50.9</v>
+        <v>175.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,49 +7283,49 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>49.43009183303574</v>
+        <v>30.5327289957459</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>12.9726055155467</v>
+        <v>27.21716625470212</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.503267227487851</v>
+        <v>0.6756847864898822</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0956344868318426</v>
+        <v>-4.793313210568286</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>4927</v>
+        <v>5607</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>遠雄港</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>365.674180642122</v>
+        <v>365.9508617738881</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>39.3</v>
+        <v>50.9</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>30.60108018974123</v>
+        <v>49.43009183303574</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>20.91014075027199</v>
+        <v>12.9726055155467</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.4427736620641327</v>
+        <v>0.503267227487851</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.5491470066057915</v>
+        <v>-0.0956344868318426</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>6153</v>
+        <v>4927</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>嘉聯益</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>363.5511784598475</v>
+        <v>365.674180642122</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>18.2</v>
+        <v>39.3</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>36.98922018546067</v>
+        <v>30.60108018974123</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>22.56020185389324</v>
+        <v>20.91014075027199</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.2458814136370511</v>
+        <v>0.4427736620641327</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.4585102992793595</v>
+        <v>-0.5491470066057915</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>6161</v>
+        <v>6153</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>363.5330846751972</v>
+        <v>363.5511784598475</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>51.7</v>
+        <v>18.2</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46.33651294515737</v>
+        <v>36.98922018546067</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>16.39795836618331</v>
+        <v>22.56020185389324</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7290901226477298</v>
+        <v>0.2458814136370511</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.1492139211055629</v>
+        <v>-0.4585102992793595</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>4967</v>
+        <v>6161</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>363.3980599465207</v>
+        <v>363.5330846751972</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>225.5</v>
+        <v>51.7</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>31.98399704426953</v>
+        <v>46.33651294515737</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>23.31311764495208</v>
+        <v>16.39795836618331</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.3499413330280743</v>
+        <v>0.7290901226477298</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-3.613345869452234</v>
+        <v>-0.1492139211055629</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>5314</v>
+        <v>4967</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>362.5799962418999</v>
+        <v>363.3980599465207</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>64.2</v>
+        <v>225.5</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,49 +7548,49 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>49.74936596163835</v>
+        <v>31.98399704426953</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>13.88842980164308</v>
+        <v>23.31311764495208</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.3525976400219187</v>
+        <v>0.3499413330280743</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.2292965907267692</v>
+        <v>-3.613345869452234</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>6126</v>
+        <v>5314</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>信音</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>357.2932301106541</v>
+        <v>362.5799962418999</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>32.45</v>
+        <v>64.2</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,49 +7601,49 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>37.35824045739717</v>
+        <v>49.74936596163835</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>22.23818880203168</v>
+        <v>13.88842980164308</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.2041945938187855</v>
+        <v>0.3525976400219187</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.5306612207122656</v>
+        <v>0.2292965907267692</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>5287</v>
+        <v>6126</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>信音</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>355.8896489965979</v>
+        <v>357.2932301106541</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>149.5</v>
+        <v>32.45</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>49.18532930916677</v>
+        <v>37.35824045739717</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>19.12053539091019</v>
+        <v>22.23818880203168</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.25741979484801</v>
+        <v>0.2041945938187855</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.0017086142721483</v>
+        <v>-0.5306612207122656</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>4571</v>
+        <v>5287</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>鈞興-KY</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>354.9943013608509</v>
+        <v>355.8896489965979</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>160</v>
+        <v>149.5</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,49 +7707,49 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>35.80506868427466</v>
+        <v>49.18532930916677</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>27.94902267636357</v>
+        <v>19.12053539091019</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.4370610322588203</v>
+        <v>0.25741979484801</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.4686791845950289</v>
+        <v>0.0017086142721483</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5309</v>
+        <v>4571</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>鈞興-KY</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>354.2523108370296</v>
+        <v>354.9943013608509</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,49 +7760,49 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>35.61057423573399</v>
+        <v>35.80506868427466</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>17.06933762518188</v>
+        <v>27.94902267636357</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.3545621242604896</v>
+        <v>0.4370610322588203</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.6991523022037587</v>
+        <v>-0.4686791845950289</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>4951</v>
+        <v>5309</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>352.4972351051782</v>
+        <v>354.2523108370296</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>82.7</v>
+        <v>58</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>26.50795417328827</v>
+        <v>35.61057423573399</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>33.71855816788337</v>
+        <v>17.06933762518188</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.3039848907867272</v>
+        <v>0.3545621242604896</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.844942010803976</v>
+        <v>-0.6991523022037587</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>4960</v>
+        <v>4951</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>350.4299933197328</v>
+        <v>352.4972351051782</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>23.2</v>
+        <v>82.7</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>32.85217658322465</v>
+        <v>26.50795417328827</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>28.04222093104056</v>
+        <v>33.71855816788337</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.3445510093657881</v>
+        <v>0.3039848907867272</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.050114488239618</v>
+        <v>-0.844942010803976</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7894,21 +7894,21 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>5355</v>
+        <v>4960</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>349.7259650070336</v>
+        <v>350.4299933197328</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>6.26</v>
+        <v>23.2</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>48.04728988310289</v>
+        <v>32.85217658322465</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>13.23954388343003</v>
+        <v>28.04222093104056</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.4133438134893289</v>
+        <v>0.3445510093657881</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.006513374015566</v>
+        <v>-0.050114488239618</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>5443</v>
+        <v>5355</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>337.2264039009644</v>
+        <v>349.7259650070336</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>108.5</v>
+        <v>6.26</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>47.09598750000877</v>
+        <v>48.04728988310289</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.18332767152557</v>
+        <v>13.23954388343003</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.8798521748090556</v>
+        <v>0.4133438134893289</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.2875739118554334</v>
+        <v>0.006513374015566</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>6120</v>
+        <v>5443</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>336.615946316528</v>
+        <v>337.2264039009644</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>14.2</v>
+        <v>108.5</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>50.15039030535225</v>
+        <v>47.09598750000877</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>9.026443102075511</v>
+        <v>17.18332767152557</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.8990091234306254</v>
+        <v>0.8798521748090556</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0438394184179884</v>
+        <v>-0.2875739118554334</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>5432</v>
+        <v>6120</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>新門</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>336.112029380814</v>
+        <v>336.615946316528</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>128.5</v>
+        <v>14.2</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>32.04410588481883</v>
+        <v>50.15039030535225</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>25.1869779023361</v>
+        <v>9.026443102075511</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.294770963710492</v>
+        <v>0.8990091234306254</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-3.598389706626544</v>
+        <v>-0.0438394184179884</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>4961</v>
+        <v>5432</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>新門</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>333.8898089978997</v>
+        <v>336.112029380814</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>168</v>
+        <v>128.5</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>47.36673104966189</v>
+        <v>32.04410588481883</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>14.17963325700457</v>
+        <v>25.1869779023361</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.5686203886526512</v>
+        <v>0.294770963710492</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.4898025045007163</v>
+        <v>-3.598389706626544</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>6133</v>
+        <v>4961</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>金橋</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>333.8587280295973</v>
+        <v>333.8898089978997</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>22.7</v>
+        <v>168</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>44.02675070030968</v>
+        <v>47.36673104966189</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>16.68985078638282</v>
+        <v>14.17963325700457</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.2515319205714655</v>
+        <v>0.5686203886526512</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.202250206332599</v>
+        <v>-0.4898025045007163</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>4440</v>
+        <v>6133</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>金橋</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>329.3961838555495</v>
+        <v>333.8587280295973</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>17.75</v>
+        <v>22.7</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>53.63032405816526</v>
+        <v>44.02675070030968</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>18.51101087469141</v>
+        <v>16.68985078638282</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.1539280288141742</v>
+        <v>0.2515319205714655</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0373155167889427</v>
+        <v>-0.202250206332599</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>4766</v>
+        <v>4440</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>328.609597366576</v>
+        <v>329.3961838555495</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>339</v>
+        <v>17.75</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>40.0836415680528</v>
+        <v>53.63032405816526</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>16.87322352274205</v>
+        <v>18.51101087469141</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.374239699281561</v>
+        <v>0.1539280288141742</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-1.732158346102784</v>
+        <v>0.0373155167889427</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>5278</v>
+        <v>4766</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>324.8225472434738</v>
+        <v>328.609597366576</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>24.75</v>
+        <v>339</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,16 +8343,16 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>54.36854392522901</v>
+        <v>40.0836415680528</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>18.53126725596876</v>
+        <v>16.87322352274205</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.07477530854897</v>
+        <v>0.374239699281561</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L149" s="2" t="n">
         <v>0</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.0304219544440162</v>
+        <v>-1.732158346102784</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>5222</v>
+        <v>5278</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>323.6376066757883</v>
+        <v>324.8225472434738</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>121.5</v>
+        <v>24.75</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>47.50736473277275</v>
+        <v>54.36854392522901</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>18.19267089934608</v>
+        <v>18.53126725596876</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.6521488003108822</v>
+        <v>1.07477530854897</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,31 +8414,31 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.26926590400412</v>
+        <v>-0.0304219544440162</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>6154</v>
+        <v>5222</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>順發</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>323.2074259036785</v>
+        <v>323.6376066757883</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>13.7</v>
+        <v>121.5</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,13 +8449,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>47.94138553632401</v>
+        <v>47.50736473277275</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>15.52528551508767</v>
+        <v>18.19267089934608</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.444603714120584</v>
+        <v>0.6521488003108822</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -8467,31 +8467,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.0275587177112306</v>
+        <v>0.26926590400412</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>4966</v>
+        <v>6154</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>順發</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>321.5961857133036</v>
+        <v>323.2074259036785</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>631</v>
+        <v>13.7</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8502,49 +8502,49 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>42.4502009216489</v>
+        <v>47.94138553632401</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>14.71477678890811</v>
+        <v>15.52528551508767</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.374333950544433</v>
+        <v>0.444603714120584</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.7882251358283447</v>
+        <v>-0.0275587177112306</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>4576</v>
+        <v>4966</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>大銀微系統</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>321.0907317001926</v>
+        <v>321.5961857133036</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>211</v>
+        <v>631</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,25 +8555,25 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>46.91817961287006</v>
+        <v>42.4502009216489</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>16.85164850742266</v>
+        <v>14.71477678890811</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.4541775425118283</v>
+        <v>0.374333950544433</v>
       </c>
       <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M153" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.9845636320048424</v>
+        <v>0.7882251358283447</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8583,21 +8583,21 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>5302</v>
+        <v>4576</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>大銀微系統</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>320.1640055376337</v>
+        <v>321.0907317001926</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>11.9</v>
+        <v>211</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,16 +8608,16 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>44.96314424464474</v>
+        <v>46.91817961287006</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>29.09663995329704</v>
+        <v>16.85164850742266</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.3759322706790872</v>
+        <v>0.4541775425118283</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" s="2" t="n">
         <v>0</v>
@@ -8626,31 +8626,31 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.2478942518471824</v>
+        <v>-0.9845636320048424</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>5381</v>
+        <v>5302</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>320.0238057149348</v>
+        <v>320.1640055376337</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>25.4</v>
+        <v>11.9</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>40.34880162863687</v>
+        <v>44.96314424464474</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>20.35309343044811</v>
+        <v>29.09663995329704</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.1733366601899756</v>
+        <v>0.3759322706790872</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.5060519392548473</v>
+        <v>-0.2478942518471824</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>5533</v>
+        <v>5381</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>皇鼎</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>314.1019669793853</v>
+        <v>320.0238057149348</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>13.8</v>
+        <v>25.4</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,16 +8714,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>44.28850976582886</v>
+        <v>40.34880162863687</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>17.79765952404696</v>
+        <v>20.35309343044811</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.5296921849481834</v>
+        <v>0.1733366601899756</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.0331428444231127</v>
+        <v>-0.5060519392548473</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>5345</v>
+        <v>5533</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>天揚</t>
+          <t>皇鼎</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>308.0013613003273</v>
+        <v>314.1019669793853</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>20.4</v>
+        <v>13.8</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>36.1749018343795</v>
+        <v>44.28850976582886</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>14.37807657917627</v>
+        <v>17.79765952404696</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.3055126001850753</v>
+        <v>0.5296921849481834</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-1.242385054826134</v>
+        <v>-0.0331428444231127</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>4934</v>
+        <v>5345</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>天揚</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>307.2453087411455</v>
+        <v>308.0013613003273</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>16.3</v>
+        <v>20.4</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,16 +8820,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>42.5470258715059</v>
+        <v>36.1749018343795</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>17.08079340117198</v>
+        <v>14.37807657917627</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.4374466979199085</v>
+        <v>0.3055126001850753</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" s="2" t="n">
         <v>0</v>
@@ -8838,31 +8838,31 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.1366892737777177</v>
+        <v>-1.242385054826134</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>4909</v>
+        <v>4934</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>307.0994709480196</v>
+        <v>307.2453087411455</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>41.15</v>
+        <v>16.3</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>31.02689951570562</v>
+        <v>42.5470258715059</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>35.74723847454401</v>
+        <v>17.08079340117198</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.4731842943305812</v>
+        <v>0.4374466979199085</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8891,31 +8891,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.1382084846474085</v>
+        <v>-0.1366892737777177</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>6113</v>
+        <v>4909</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>亞矽</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>304.2916595042016</v>
+        <v>307.0994709480196</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>24.6</v>
+        <v>41.15</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,16 +8926,16 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>41.9620964543093</v>
+        <v>31.02689951570562</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>21.2956760331517</v>
+        <v>35.74723847454401</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.3324743697202095</v>
+        <v>0.4731842943305812</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L160" s="2" t="n">
         <v>0</v>
@@ -8944,31 +8944,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.2821226466216285</v>
+        <v>-0.1382084846474085</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>5227</v>
+        <v>6113</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>立凱-KY</t>
+          <t>亞矽</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>302.0275805956267</v>
+        <v>304.2916595042016</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>31.25</v>
+        <v>24.6</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8979,13 +8979,13 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>46.56665254389002</v>
+        <v>41.9620964543093</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>22.22527009255546</v>
+        <v>21.2956760331517</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.8722802772654402</v>
+        <v>0.3324743697202095</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.9435221780338658</v>
+        <v>-0.2821226466216285</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>6136</v>
+        <v>5227</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>立凱-KY</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>301.1238876669393</v>
+        <v>302.0275805956267</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>24.35</v>
+        <v>31.25</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,13 +9032,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>41.50299697701622</v>
+        <v>46.56665254389002</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>23.42077344623069</v>
+        <v>22.22527009255546</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.3792218701777773</v>
+        <v>0.8722802772654402</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>0</v>
@@ -9050,31 +9050,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.0235148281025703</v>
+        <v>-0.9435221780338658</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>5608</v>
+        <v>6136</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>四維航</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>298.898574267631</v>
+        <v>301.1238876669393</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>14.3</v>
+        <v>24.35</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>44.92529389860402</v>
+        <v>41.50299697701622</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>12.84295149970184</v>
+        <v>23.42077344623069</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.3261984838803063</v>
+        <v>0.3792218701777773</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.0079125545235378</v>
+        <v>-0.0235148281025703</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>5474</v>
+        <v>5608</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>聰泰</t>
+          <t>四維航</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>296.2820136114058</v>
+        <v>298.898574267631</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>151.5</v>
+        <v>14.3</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,13 +9138,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>37.75853775395756</v>
+        <v>44.92529389860402</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>15.5395330609028</v>
+        <v>12.84295149970184</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.2491417124475818</v>
+        <v>0.3261984838803063</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-1.952277949614519</v>
+        <v>-0.0079125545235378</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>6112</v>
+        <v>5474</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>聰泰</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>296.0141747002939</v>
+        <v>296.2820136114058</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>42.25</v>
+        <v>151.5</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>38.19851420863597</v>
+        <v>37.75853775395756</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>22.58169838696464</v>
+        <v>15.5395330609028</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.7611624325558261</v>
+        <v>0.2491417124475818</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.1548130905569634</v>
+        <v>-1.952277949614519</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>5498</v>
+        <v>6112</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>凱崴</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>295.1162768768008</v>
+        <v>296.0141747002939</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>54</v>
+        <v>42.25</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>35.18112232684992</v>
+        <v>38.19851420863597</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>15.88822411281795</v>
+        <v>22.58169838696464</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.4651484482516062</v>
+        <v>0.7611624325558261</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>0</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.5694893710703144</v>
+        <v>-0.1548130905569634</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>6114</v>
+        <v>5498</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>久威</t>
+          <t>凱崴</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>287.8481554943357</v>
+        <v>295.1162768768008</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>29.05</v>
+        <v>54</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>44.34698870686599</v>
+        <v>35.18112232684992</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>19.19009764795556</v>
+        <v>15.88822411281795</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.1764354040797238</v>
+        <v>0.4651484482516062</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.2317668428001276</v>
+        <v>-0.5694893710703144</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>4763</v>
+        <v>6114</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>久威</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>286.9602958349656</v>
+        <v>287.8481554943357</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>47.45</v>
+        <v>29.05</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,49 +9350,49 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>53.63230876888138</v>
+        <v>44.34698870686599</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>19.64312791323869</v>
+        <v>19.19009764795556</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.361038269699545</v>
+        <v>0.1764354040797238</v>
       </c>
       <c r="K168" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.2721895007889365</v>
+        <v>-0.2317668428001276</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>5220</v>
+        <v>4763</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>286.6918850973588</v>
+        <v>286.9602958349656</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>21.05</v>
+        <v>47.45</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,49 +9403,49 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>48.43112932887485</v>
+        <v>53.63230876888138</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>18.39639085053792</v>
+        <v>19.64312791323869</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.5909748704083099</v>
+        <v>0.361038269699545</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.0419574368537267</v>
+        <v>-0.2721895007889365</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>5340</v>
+        <v>5220</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>283.2752851108879</v>
+        <v>286.6918850973588</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>77.7</v>
+        <v>21.05</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>33.92293127931329</v>
+        <v>48.43112932887485</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>15.56250452475302</v>
+        <v>18.39639085053792</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.3501750190160633</v>
+        <v>0.5909748704083099</v>
       </c>
       <c r="K170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.8476800006778316</v>
+        <v>0.0419574368537267</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>4912</v>
+        <v>5340</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>282.2271008602008</v>
+        <v>283.2752851108879</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>87.5</v>
+        <v>77.7</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>46.79290004805762</v>
+        <v>33.92293127931329</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>18.9302271269602</v>
+        <v>15.56250452475302</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.8320747029845525</v>
+        <v>0.3501750190160633</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.386610669913594</v>
+        <v>-0.8476800006778316</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>4931</v>
+        <v>4912</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>281.7025927695666</v>
+        <v>282.2271008602008</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>221</v>
+        <v>87.5</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,16 +9562,16 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>43.69891400100806</v>
+        <v>46.79290004805762</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>19.33292093510086</v>
+        <v>18.9302271269602</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.3716938497635811</v>
+        <v>0.8320747029845525</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-4.891249578467095</v>
+        <v>0.386610669913594</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>5452</v>
+        <v>4931</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>佶優</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>275.9743164321326</v>
+        <v>281.7025927695666</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>28.85</v>
+        <v>221</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>35.76117936058759</v>
+        <v>43.69891400100806</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>13.55030810190116</v>
+        <v>19.33292093510086</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.3228216016729922</v>
+        <v>0.3716938497635811</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.5282138891627194</v>
+        <v>-4.891249578467095</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9643,21 +9643,21 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>4441</v>
+        <v>5452</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>振大環球</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>274.5534088863293</v>
+        <v>275.9743164321326</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>180.5</v>
+        <v>28.85</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,16 +9668,16 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>33.49133422844756</v>
+        <v>35.76117936058759</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>13.50588267591902</v>
+        <v>13.55030810190116</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>3.299049760666314</v>
+        <v>0.3228216016729922</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L174" s="2" t="n">
         <v>0</v>
@@ -9686,31 +9686,31 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.8048713807938541</v>
+        <v>-0.5282138891627194</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>4746</v>
+        <v>4441</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>振大環球</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>273.5382990715623</v>
+        <v>274.5534088863293</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>53</v>
+        <v>180.5</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,16 +9721,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>48.43932523123419</v>
+        <v>33.49133422844756</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>13.84166745094573</v>
+        <v>13.50588267591902</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.3164207517131203</v>
+        <v>3.299049760666314</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -9739,31 +9739,31 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.0853138148297844</v>
+        <v>-0.8048713807938541</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>5251</v>
+        <v>4746</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>268.0801828199735</v>
+        <v>273.5382990715623</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>27.8</v>
+        <v>53</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>38.80136565821593</v>
+        <v>48.43932523123419</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>27.5177092410779</v>
+        <v>13.84166745094573</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.3424026684154826</v>
+        <v>0.3164207517131203</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.4861048609919977</v>
+        <v>-0.0853138148297844</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>5344</v>
+        <v>5251</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>265.9633636657284</v>
+        <v>268.0801828199735</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>15.8</v>
+        <v>27.8</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,13 +9827,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>47.69562883644642</v>
+        <v>38.80136565821593</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>16.45187448952879</v>
+        <v>27.5177092410779</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.0801465810179066</v>
+        <v>0.3424026684154826</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.037531321072248</v>
+        <v>-0.4861048609919977</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>4977</v>
+        <v>5344</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>261.0012982741618</v>
+        <v>265.9633636657284</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>144</v>
+        <v>15.8</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>35.05069814205459</v>
+        <v>47.69562883644642</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>15.68914334291429</v>
+        <v>16.45187448952879</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.4683892394967517</v>
+        <v>0.0801465810179066</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.6406502175049233</v>
+        <v>-0.037531321072248</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>4588</v>
+        <v>4977</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>256.5249087224778</v>
+        <v>261.0012982741618</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>54.2</v>
+        <v>144</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>38.81956572419625</v>
+        <v>35.05069814205459</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>14.82572544843954</v>
+        <v>15.68914334291429</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.4528413613475306</v>
+        <v>0.4683892394967517</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>0</v>
@@ -9951,31 +9951,31 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.5710117286947489</v>
+        <v>-0.6406502175049233</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>4919</v>
+        <v>4588</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>255.3501612070193</v>
+        <v>256.5249087224778</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>156.5</v>
+        <v>54.2</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -9986,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>42.84903303910433</v>
+        <v>38.81956572419625</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>13.58693439217329</v>
+        <v>14.82572544843954</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.5565332921535421</v>
+        <v>0.4528413613475306</v>
       </c>
       <c r="K180" s="2" t="n">
         <v>0</v>
@@ -10004,31 +10004,31 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-2.054758902872106</v>
+        <v>-0.5710117286947489</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>5386</v>
+        <v>4919</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>254.5819972165703</v>
+        <v>255.3501612070193</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>383</v>
+        <v>156.5</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -10039,16 +10039,16 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>40.16047588708804</v>
+        <v>42.84903303910433</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>16.44316895560161</v>
+        <v>13.58693439217329</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.8824867125052117</v>
+        <v>0.5565332921535421</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L181" s="2" t="n">
         <v>0</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-9.936210158095475</v>
+        <v>-2.054758902872106</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10067,21 +10067,21 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>4903</v>
+        <v>5386</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>254.3637129843631</v>
+        <v>254.5819972165703</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>38.5</v>
+        <v>383</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -10092,16 +10092,16 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>42.39495893145978</v>
+        <v>40.16047588708804</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>11.7103092122464</v>
+        <v>16.44316895560161</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.2756023110478063</v>
+        <v>0.8824867125052117</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" s="2" t="n">
         <v>0</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.0019330309941983</v>
+        <v>-9.936210158095475</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10120,21 +10120,21 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>4972</v>
+        <v>4903</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>253.7993204369403</v>
+        <v>254.3637129843631</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>16.85</v>
+        <v>38.5</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10145,13 +10145,13 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>48.99706951359516</v>
+        <v>42.39495893145978</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>31.29620299498247</v>
+        <v>11.7103092122464</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.5830680026143321</v>
+        <v>0.2756023110478063</v>
       </c>
       <c r="K183" s="2" t="n">
         <v>0</v>
@@ -10163,31 +10163,31 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.0285233204891246</v>
+        <v>0.0019330309941983</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>5243</v>
+        <v>4972</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>253.69284078001</v>
+        <v>253.7993204369403</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>96</v>
+        <v>16.85</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10198,13 +10198,13 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>41.26637933497093</v>
+        <v>48.99706951359516</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>15.98020022032479</v>
+        <v>31.29620299498247</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.7639644186184212</v>
+        <v>0.5830680026143321</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
@@ -10216,31 +10216,31 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.2610316092315514</v>
+        <v>-0.0285233204891246</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>5292</v>
+        <v>5243</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>253.2571180568328</v>
+        <v>253.69284078001</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>174.5</v>
+        <v>96</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -10251,13 +10251,13 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>28.35390243770844</v>
+        <v>41.26637933497093</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>22.98884874986657</v>
+        <v>15.98020022032479</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.3628225116411487</v>
+        <v>0.7639644186184212</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
@@ -10269,31 +10269,31 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-5.287095664708029</v>
+        <v>-0.2610316092315514</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>6147</v>
+        <v>5292</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>252.2826251108904</v>
+        <v>253.2571180568328</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>198</v>
+        <v>174.5</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -10304,13 +10304,13 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>43.47654622994456</v>
+        <v>28.35390243770844</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>14.61949914590648</v>
+        <v>22.98884874986657</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.6595538070698401</v>
+        <v>0.3628225116411487</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>0</v>
@@ -10322,31 +10322,31 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-3.141553368878368</v>
+        <v>-5.287095664708029</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>4749</v>
+        <v>6147</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>250.6329988495173</v>
+        <v>252.2826251108904</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>860</v>
+        <v>198</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,13 +10357,13 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>40.778946297856</v>
+        <v>43.47654622994456</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>17.37832979468719</v>
+        <v>14.61949914590648</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.5049909180910277</v>
+        <v>0.6595538070698401</v>
       </c>
       <c r="K187" s="2" t="n">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-1.262871437728052</v>
+        <v>-3.141553368878368</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10385,21 +10385,21 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>5493</v>
+        <v>4749</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>250.1908383774532</v>
+        <v>250.6329988495173</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>83.8</v>
+        <v>860</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>36.35362775150647</v>
+        <v>40.778946297856</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>16.11651284433352</v>
+        <v>17.37832979468719</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.5543331924980128</v>
+        <v>0.5049909180910277</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188" s="2" t="n">
         <v>0</v>
@@ -10428,31 +10428,31 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.9317412847443964</v>
+        <v>-1.262871437728052</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>5438</v>
+        <v>5493</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>249.1356665788314</v>
+        <v>250.1908383774532</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>18.85</v>
+        <v>83.8</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>47.29810312031533</v>
+        <v>36.35362775150647</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>16.89176593632055</v>
+        <v>16.11651284433352</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.5165837014915666</v>
+        <v>0.5543331924980128</v>
       </c>
       <c r="K189" s="2" t="n">
         <v>2</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0182564389252662</v>
+        <v>-0.9317412847443964</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>4930</v>
+        <v>5438</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>燦星網</t>
+          <t>東友</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>244.016529158298</v>
+        <v>249.1356665788314</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>17</v>
+        <v>18.85</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>44.74656997823824</v>
+        <v>47.29810312031533</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>19.3951359347798</v>
+        <v>16.89176593632055</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.321251732667378</v>
+        <v>0.5165837014915666</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>2</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.0148959451074873</v>
+        <v>-0.0182564389252662</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>4906</v>
+        <v>4930</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>燦星網</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>241.9803143336972</v>
+        <v>244.016529158298</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>37.75</v>
+        <v>17</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,16 +10569,16 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>39.19279707231274</v>
+        <v>44.74656997823824</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>16.80906699056163</v>
+        <v>19.3951359347798</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.3498254035677619</v>
+        <v>0.321251732667378</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.5544094697367286</v>
+        <v>0.0148959451074873</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>6108</v>
+        <v>4906</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>241.5931839651085</v>
+        <v>241.9803143336972</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>17.45</v>
+        <v>37.75</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,13 +10622,13 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>38.95762059615851</v>
+        <v>39.19279707231274</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>11.20517586017661</v>
+        <v>16.80906699056163</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.8651298178307837</v>
+        <v>0.3498254035677619</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.1045123508829709</v>
+        <v>-0.5544094697367286</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>5348</v>
+        <v>6108</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>241.5913619326451</v>
+        <v>241.5931839651085</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>15.55</v>
+        <v>17.45</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>50.21231352826636</v>
+        <v>38.95762059615851</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>7.837209354626917</v>
+        <v>11.20517586017661</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.2533874478243549</v>
+        <v>0.8651298178307837</v>
       </c>
       <c r="K193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.006836722790364</v>
+        <v>-0.1045123508829709</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>4956</v>
+        <v>5348</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>240.7300255710715</v>
+        <v>241.5913619326451</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>32.55</v>
+        <v>15.55</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>32.54871068415908</v>
+        <v>50.21231352826636</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>14.15588214377598</v>
+        <v>7.837209354626917</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.3099825791273325</v>
+        <v>0.2533874478243549</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.4289560168369459</v>
+        <v>-0.006836722790364</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>4552</v>
+        <v>4956</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>力達-KY</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>238.8421899458733</v>
+        <v>240.7300255710715</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>19.55</v>
+        <v>32.55</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,16 +10781,16 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>38.45696363562563</v>
+        <v>32.54871068415908</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>27.41080038769457</v>
+        <v>14.15588214377598</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.5187401762433497</v>
+        <v>0.3099825791273325</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.0873539493555955</v>
+        <v>-0.4289560168369459</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>5203</v>
+        <v>4552</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>力達-KY</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>237.7796003781277</v>
+        <v>238.8421899458733</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>19.55</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,16 +10834,16 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>47.31950238292401</v>
+        <v>38.45696363562563</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>16.01850906159914</v>
+        <v>27.41080038769457</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.2688258024444201</v>
+        <v>0.5187401762433497</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L196" s="2" t="n">
         <v>0</v>
@@ -10852,31 +10852,31 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.2326647190676144</v>
+        <v>-0.0873539493555955</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>6151</v>
+        <v>5203</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>晉倫</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>237.3741355754217</v>
+        <v>237.7796003781277</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>37.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,13 +10887,13 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>38.53771821596111</v>
+        <v>47.31950238292401</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>16.05581412726288</v>
+        <v>16.01850906159914</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.5335029613754672</v>
+        <v>0.2688258024444201</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.1412579752824889</v>
+        <v>-0.2326647190676144</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>4994</v>
+        <v>6151</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>晉倫</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>236.0199250965923</v>
+        <v>237.3741355754217</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>91.7</v>
+        <v>37.7</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>53.2122953213666</v>
+        <v>38.53771821596111</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>28.0309037379715</v>
+        <v>16.05581412726288</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.6252317069740922</v>
+        <v>0.5335029613754672</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -10958,31 +10958,31 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.1342035023326266</v>
+        <v>-0.1412579752824889</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>5907</v>
+        <v>4994</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>大洋-KY</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>233.5334099074177</v>
+        <v>236.0199250965923</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>4.93</v>
+        <v>91.7</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,16 +10993,16 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>45.62363629716336</v>
+        <v>53.2122953213666</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>13.44915185129391</v>
+        <v>28.0309037379715</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.861452229675164</v>
+        <v>0.6252317069740922</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L199" s="2" t="n">
         <v>0</v>
@@ -11011,31 +11011,31 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0013328397044075</v>
+        <v>0.1342035023326266</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>6125</v>
+        <v>5907</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>大洋-KY</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>232.1848151702061</v>
+        <v>233.5334099074177</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>54.8</v>
+        <v>4.93</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,16 +11046,16 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>35.94208722435224</v>
+        <v>45.62363629716336</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>17.10642593961215</v>
+        <v>13.44915185129391</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.4553845148454462</v>
+        <v>0.861452229675164</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L200" s="2" t="n">
         <v>0</v>
@@ -11064,31 +11064,31 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.4141907596239194</v>
+        <v>-0.0013328397044075</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>6134</v>
+        <v>6125</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>萬旭</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>230.0197191572917</v>
+        <v>232.1848151702061</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>28.15</v>
+        <v>54.8</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>33.74241019917635</v>
+        <v>35.94208722435224</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>17.33786417530401</v>
+        <v>17.10642593961215</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.3932002641271782</v>
+        <v>0.4553845148454462</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
@@ -11117,31 +11117,31 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.7053688057443306</v>
+        <v>-0.4141907596239194</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>6152</v>
+        <v>6134</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>萬旭</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>229.9704199623552</v>
+        <v>230.0197191572917</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>12.65</v>
+        <v>28.15</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>36.76361143729293</v>
+        <v>33.74241019917635</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>13.82747480354288</v>
+        <v>17.33786417530401</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.8647681571552012</v>
+        <v>0.3932002641271782</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.0209383850073474</v>
+        <v>-0.7053688057443306</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11180,21 +11180,21 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>5244</v>
+        <v>6152</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>229.0335225950947</v>
+        <v>229.9704199623552</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>33.1</v>
+        <v>12.65</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,13 +11205,13 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>28.59986736771678</v>
+        <v>36.76361143729293</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>27.19508273850972</v>
+        <v>13.82747480354288</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.4765261187680789</v>
+        <v>0.8647681571552012</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
@@ -11223,31 +11223,31 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.2158174346408921</v>
+        <v>-0.0209383850073474</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>5356</v>
+        <v>5244</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>227.8893480441667</v>
+        <v>229.0335225950947</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>25.2</v>
+        <v>33.1</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,13 +11258,13 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>29.54157881202421</v>
+        <v>28.59986736771678</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>19.83533814819127</v>
+        <v>27.19508273850972</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.4702471583898067</v>
+        <v>0.4765261187680789</v>
       </c>
       <c r="K204" s="2" t="n">
         <v>0</v>
@@ -11276,31 +11276,31 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.3001332820784715</v>
+        <v>-0.2158174346408921</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>6115</v>
+        <v>5356</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>221.9563544043597</v>
+        <v>227.8893480441667</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>45.7</v>
+        <v>25.2</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,13 +11311,13 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>32.64892479941042</v>
+        <v>29.54157881202421</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>17.51081231628605</v>
+        <v>19.83533814819127</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.6245798483221321</v>
+        <v>0.4702471583898067</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.3523327496008799</v>
+        <v>-0.3001332820784715</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11339,21 +11339,21 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>5205</v>
+        <v>6115</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>217.3662190535093</v>
+        <v>221.9563544043597</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>21.45</v>
+        <v>45.7</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,13 +11364,13 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>49.44791990538062</v>
+        <v>32.64892479941042</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>27.30603405586233</v>
+        <v>17.51081231628605</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>1.40586310058506</v>
+        <v>0.6245798483221321</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>0</v>
@@ -11382,31 +11382,31 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.661139596284939</v>
+        <v>-0.3523327496008799</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>6104</v>
+        <v>5205</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>216.5172990772517</v>
+        <v>217.3662190535093</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>97.2</v>
+        <v>21.45</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,13 +11417,13 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>42.13648208607908</v>
+        <v>49.44791990538062</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>9.483790914072459</v>
+        <v>27.30603405586233</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.8697637793129285</v>
+        <v>1.40586310058506</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>0</v>
@@ -11435,31 +11435,31 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.6177503703056342</v>
+        <v>-0.661139596284939</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>5215</v>
+        <v>6104</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>213.4059735249845</v>
+        <v>216.5172990772517</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>40.45</v>
+        <v>97.2</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -11470,13 +11470,13 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>35.36296263403166</v>
+        <v>42.13648208607908</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>18.8826834740868</v>
+        <v>9.483790914072459</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.4734537109307624</v>
+        <v>0.8697637793129285</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>0</v>
@@ -11488,31 +11488,31 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.4947229544399939</v>
+        <v>-0.6177503703056342</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>4569</v>
+        <v>5215</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>210.85047737379</v>
+        <v>213.4059735249845</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>167.5</v>
+        <v>40.45</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -11523,16 +11523,16 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>45.78903216407277</v>
+        <v>35.36296263403166</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>13.94267449948323</v>
+        <v>18.8826834740868</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.4406003887909025</v>
+        <v>0.4734537109307624</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L209" s="2" t="n">
         <v>0</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.8593581773766856</v>
+        <v>-0.4947229544399939</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11551,21 +11551,21 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>6123</v>
+        <v>4569</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>207.728270187717</v>
+        <v>210.85047737379</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>42.4</v>
+        <v>167.5</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -11576,13 +11576,13 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>46.05967274111441</v>
+        <v>45.78903216407277</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>15.30441774245353</v>
+        <v>13.94267449948323</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>0.6753662237819658</v>
+        <v>0.4406003887909025</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>2</v>
@@ -11594,31 +11594,31 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.1024455180264699</v>
+        <v>-0.8593581773766856</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>4949</v>
+        <v>6123</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>206.9115705728853</v>
+        <v>207.728270187717</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>76.7</v>
+        <v>42.4</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>41.20984881702558</v>
+        <v>46.05967274111441</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>19.41708027575288</v>
+        <v>15.30441774245353</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.4580832588740536</v>
+        <v>0.6753662237819658</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>0</v>
@@ -11647,31 +11647,31 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.2389135106443065</v>
+        <v>0.1024455180264699</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>5706</v>
+        <v>4949</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>鳳凰</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>199.6604024791013</v>
+        <v>206.9115705728853</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>46.95</v>
+        <v>76.7</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -11682,16 +11682,16 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>33.9322410110463</v>
+        <v>41.20984881702558</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>29.31007079833695</v>
+        <v>19.41708027575288</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.3740279349191621</v>
+        <v>0.4580832588740536</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>0</v>
@@ -11700,31 +11700,31 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.1751507921548643</v>
+        <v>0.2389135106443065</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>6128</v>
+        <v>5706</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>上福</t>
+          <t>鳳凰</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>197.8113948801501</v>
+        <v>199.6604024791013</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>20.6</v>
+        <v>46.95</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -11735,16 +11735,16 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>52.77441022510498</v>
+        <v>33.9322410110463</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>13.25923683141783</v>
+        <v>29.31007079833695</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.5473503234046215</v>
+        <v>0.3740279349191621</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L213" s="2" t="n">
         <v>0</v>
@@ -11753,31 +11753,31 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.0138783332687048</v>
+        <v>-0.1751507921548643</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>4968</v>
+        <v>6128</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>上福</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>197.2684473438082</v>
+        <v>197.8113948801501</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>104</v>
+        <v>20.6</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,13 +11788,13 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>36.78597129058358</v>
+        <v>52.77441022510498</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>14.08752317732538</v>
+        <v>13.25923683141783</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.5674201904634847</v>
+        <v>0.5473503234046215</v>
       </c>
       <c r="K214" s="2" t="n">
         <v>0</v>
@@ -11806,31 +11806,31 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-1.173071320668462</v>
+        <v>-0.0138783332687048</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>4729</v>
+        <v>4968</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>196.1009075102647</v>
+        <v>197.2684473438082</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>20.1</v>
+        <v>104</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>38.9359427724406</v>
+        <v>36.78597129058358</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>17.27819894247236</v>
+        <v>14.08752317732538</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.35572840805457</v>
+        <v>0.5674201904634847</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
@@ -11859,31 +11859,31 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.2714953873740012</v>
+        <v>-1.173071320668462</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>6117</v>
+        <v>4729</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>194.9859105974774</v>
+        <v>196.1009075102647</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>20.1</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,13 +11894,13 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>31.43842398180362</v>
+        <v>38.9359427724406</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>25.24111212303293</v>
+        <v>17.27819894247236</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.6811538291352781</v>
+        <v>0.35572840805457</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
@@ -11912,31 +11912,31 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.3157525556457794</v>
+        <v>-0.2714953873740012</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>5315</v>
+        <v>6117</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>迎廣</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>191.7542209337085</v>
+        <v>194.9859105974774</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>19.85</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,13 +11947,13 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>27.24410325764268</v>
+        <v>31.43842398180362</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>30.24354934806749</v>
+        <v>25.24111212303293</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.3754220933708566</v>
+        <v>0.6811538291352781</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.2808816161694711</v>
+        <v>-0.3157525556457794</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>5236</v>
+        <v>5315</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>188.3907406079507</v>
+        <v>191.7542209337085</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>152.5</v>
+        <v>19.85</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>35.9220641367892</v>
+        <v>27.24410325764268</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>19.72581252538362</v>
+        <v>30.24354934806749</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.4873311693784834</v>
+        <v>0.3754220933708566</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>0</v>
@@ -12018,31 +12018,31 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-1.712605058664143</v>
+        <v>-0.2808816161694711</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>5245</v>
+        <v>5236</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>186.6875739760904</v>
+        <v>188.3907406079507</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>25.35</v>
+        <v>152.5</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -12053,13 +12053,13 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>40.41687975957919</v>
+        <v>35.9220641367892</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>19.05376814818729</v>
+        <v>19.72581252538362</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>0.5789911831951257</v>
+        <v>0.4873311693784834</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.1910996589097661</v>
+        <v>-1.712605058664143</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12081,21 +12081,21 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>4905</v>
+        <v>5245</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>185.3070625337021</v>
+        <v>186.6875739760904</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>69.8</v>
+        <v>25.35</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -12106,13 +12106,13 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>51.51485734114751</v>
+        <v>40.41687975957919</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>14.43163258089357</v>
+        <v>19.05376814818729</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>0.8701484801365895</v>
+        <v>0.5789911831951257</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>0</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>1.616489442434487</v>
+        <v>-0.1910996589097661</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>4943</v>
+        <v>4905</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>181.6058999112609</v>
+        <v>185.3070625337021</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>8.69</v>
+        <v>69.8</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -12159,13 +12159,13 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>45.06584443711948</v>
+        <v>51.51485734114751</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>13.27869511171834</v>
+        <v>14.43163258089357</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.5491652604295338</v>
+        <v>0.8701484801365895</v>
       </c>
       <c r="K221" s="2" t="n">
         <v>0</v>
@@ -12177,31 +12177,31 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.0422680038640262</v>
+        <v>1.616489442434487</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>4737</v>
+        <v>4943</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>華廣</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>180.3002703743274</v>
+        <v>181.6058999112609</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>56.6</v>
+        <v>8.69</v>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
@@ -12212,13 +12212,13 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>46.76122912019332</v>
+        <v>45.06584443711948</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>18.52173461277052</v>
+        <v>13.27869511171834</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>0.930027037432738</v>
+        <v>0.5491652604295338</v>
       </c>
       <c r="K222" s="2" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.2388309516038119</v>
+        <v>-0.0422680038640262</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12240,21 +12240,21 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>4933</v>
+        <v>4737</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>華廣</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>165.7400147753899</v>
+        <v>180.3002703743274</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>59.7</v>
+        <v>56.6</v>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
@@ -12265,13 +12265,13 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>31.27731261105153</v>
+        <v>46.76122912019332</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>18.13761370917855</v>
+        <v>18.52173461277052</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>0.5002055081918161</v>
+        <v>0.930027037432738</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>0</v>
@@ -12283,31 +12283,31 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.6806942697052343</v>
+        <v>0.2388309516038119</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>4974</v>
+        <v>4933</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
         <v/>
       </c>
       <c r="D224" s="2" t="n">
-        <v>163.3996479445393</v>
+        <v>165.7400147753899</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>69.5</v>
+        <v>59.7</v>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
@@ -12318,16 +12318,16 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>41.78122524882811</v>
+        <v>31.27731261105153</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>16.31181266231642</v>
+        <v>18.13761370917855</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>0.4459628351830925</v>
+        <v>0.5002055081918161</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L224" s="2" t="n">
         <v>0</v>
@@ -12336,31 +12336,31 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.0782900479017072</v>
+        <v>-0.6806942697052343</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>6124</v>
+        <v>4974</v>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>業強</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
         <v/>
       </c>
       <c r="D225" s="2" t="n">
-        <v>158.0264701852113</v>
+        <v>163.3996479445393</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>27.75</v>
+        <v>69.5</v>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
@@ -12371,16 +12371,16 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>38.07977967192676</v>
+        <v>41.78122524882811</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>18.66435748713156</v>
+        <v>16.31181266231642</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>0.3980973467476065</v>
+        <v>0.4459628351830925</v>
       </c>
       <c r="K225" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L225" s="2" t="n">
         <v>0</v>
@@ -12389,31 +12389,31 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>-0.2497328562630902</v>
+        <v>0.0782900479017072</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>6150</v>
+        <v>6124</v>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>撼訊</t>
+          <t>業強</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
         <v/>
       </c>
       <c r="D226" s="2" t="n">
-        <v>153.3322020458164</v>
+        <v>158.0264701852113</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>60.4</v>
+        <v>27.75</v>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
@@ -12424,13 +12424,13 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>43.30144687699914</v>
+        <v>38.07977967192676</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>12.79171226640934</v>
+        <v>18.66435748713156</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>0.6218300818763896</v>
+        <v>0.3980973467476065</v>
       </c>
       <c r="K226" s="2" t="n">
         <v>0</v>
@@ -12442,31 +12442,31 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>-0.0432222018440663</v>
+        <v>-0.2497328562630902</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>4562</v>
+        <v>6150</v>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>穎漢</t>
+          <t>撼訊</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
         <v/>
       </c>
       <c r="D227" s="2" t="n">
-        <v>146.3066183591363</v>
+        <v>153.3322020458164</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>33.3</v>
+        <v>60.4</v>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
@@ -12477,16 +12477,16 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>40.94808199097246</v>
+        <v>43.30144687699914</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>11.48636486211212</v>
+        <v>12.79171226640934</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>0.3361695454395192</v>
+        <v>0.6218300818763896</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L227" s="2" t="n">
         <v>0</v>
@@ -12495,31 +12495,31 @@
         <v>-1</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>-0.0275152110183807</v>
+        <v>-0.0432222018440663</v>
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>5225</v>
+        <v>4562</v>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>穎漢</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
         <v/>
       </c>
       <c r="D228" s="2" t="n">
-        <v>141.9511429029584</v>
+        <v>146.3066183591363</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>33.3</v>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
@@ -12530,16 +12530,16 @@
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>44.7368244168143</v>
+        <v>40.94808199097246</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>14.98576415361382</v>
+        <v>11.48636486211212</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>0.2972329331021177</v>
+        <v>0.3361695454395192</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228" s="2" t="n">
         <v>0</v>
@@ -12548,31 +12548,31 @@
         <v>-1</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>-0.1954925717506695</v>
+        <v>-0.0275152110183807</v>
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>6118</v>
+        <v>5225</v>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
         <v/>
       </c>
       <c r="D229" s="2" t="n">
-        <v>133.8009143740238</v>
+        <v>141.9511429029584</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>16.95</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
@@ -12583,16 +12583,16 @@
         <v>0</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>47.98569538593824</v>
+        <v>44.7368244168143</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>15.55379489744215</v>
+        <v>14.98576415361382</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>0.6261650430850723</v>
+        <v>0.2972329331021177</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L229" s="2" t="n">
         <v>0</v>
@@ -12601,7 +12601,7 @@
         <v>-1</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>0.0272645508736031</v>
+        <v>-0.1954925717506695</v>
       </c>
       <c r="O229" s="2" t="inlineStr">
         <is>
@@ -12611,21 +12611,21 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>5457</v>
+        <v>6118</v>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>建達</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
         <v/>
       </c>
       <c r="D230" s="2" t="n">
-        <v>130.8658859888576</v>
+        <v>133.8009143740238</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>31.4</v>
+        <v>16.95</v>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
@@ -12636,16 +12636,16 @@
         <v>0</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>40.0018935185298</v>
+        <v>47.98569538593824</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>17.45303096121464</v>
+        <v>15.55379489744215</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>0.3484502072781717</v>
+        <v>0.6261650430850723</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L230" s="2" t="n">
         <v>0</v>
@@ -12654,7 +12654,7 @@
         <v>-1</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>-0.4831450120497312</v>
+        <v>0.0272645508736031</v>
       </c>
       <c r="O230" s="2" t="inlineStr">
         <is>
@@ -12664,21 +12664,21 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>5531</v>
+        <v>5457</v>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>鄉林</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
         <v/>
       </c>
       <c r="D231" s="2" t="n">
-        <v>112.4995804400679</v>
+        <v>130.8658859888576</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>7.9</v>
+        <v>31.4</v>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
@@ -12689,13 +12689,13 @@
         <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>46.26273141626685</v>
+        <v>40.0018935185298</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>17.86535425152574</v>
+        <v>17.45303096121464</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>0.8847887445921528</v>
+        <v>0.3484502072781717</v>
       </c>
       <c r="K231" s="2" t="n">
         <v>0</v>
@@ -12707,7 +12707,7 @@
         <v>-1</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>-0.009085331500970399</v>
+        <v>-0.4831450120497312</v>
       </c>
       <c r="O231" s="2" t="inlineStr">
         <is>
@@ -12717,21 +12717,21 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>5272</v>
+        <v>5531</v>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>鄉林</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
         <v/>
       </c>
       <c r="D232" s="2" t="n">
-        <v>107.045232800443</v>
+        <v>112.4995804400679</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>19.7</v>
+        <v>7.9</v>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
@@ -12742,13 +12742,13 @@
         <v>0</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>37.92554779821443</v>
+        <v>46.26273141626685</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>12.02293631861898</v>
+        <v>17.86535425152574</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>0.7000862846799965</v>
+        <v>0.8847887445921528</v>
       </c>
       <c r="K232" s="2" t="n">
         <v>0</v>
@@ -12760,7 +12760,7 @@
         <v>-1</v>
       </c>
       <c r="N232" s="2" t="n">
-        <v>-0.0839184306691617</v>
+        <v>-0.009085331500970399</v>
       </c>
       <c r="O232" s="2" t="inlineStr">
         <is>
@@ -12770,21 +12770,21 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>5521</v>
+        <v>5272</v>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>工信</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
         <v/>
       </c>
       <c r="D233" s="2" t="n">
-        <v>100.0831519270968</v>
+        <v>107.045232800443</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>10.35</v>
+        <v>19.7</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -12795,13 +12795,13 @@
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>46.92466644425804</v>
+        <v>37.92554779821443</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>15.32797521890133</v>
+        <v>12.02293631861898</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>0.6908620587632238</v>
+        <v>0.7000862846799965</v>
       </c>
       <c r="K233" s="2" t="n">
         <v>0</v>
@@ -12813,7 +12813,7 @@
         <v>-1</v>
       </c>
       <c r="N233" s="2" t="n">
-        <v>0.0135418981495234</v>
+        <v>-0.0839184306691617</v>
       </c>
       <c r="O233" s="2" t="inlineStr">
         <is>
@@ -12823,21 +12823,21 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>5223</v>
+        <v>5521</v>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
         <v/>
       </c>
       <c r="D234" s="2" t="n">
-        <v>90.74386851768108</v>
+        <v>100.0831519270968</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>24.55</v>
+        <v>10.35</v>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
@@ -12848,13 +12848,13 @@
         <v>0</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>45.06435526381252</v>
+        <v>46.92466644425804</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>15.04137883517502</v>
+        <v>15.32797521890133</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>0.0875314323301747</v>
+        <v>0.6908620587632238</v>
       </c>
       <c r="K234" s="2" t="n">
         <v>0</v>
@@ -12866,7 +12866,7 @@
         <v>-1</v>
       </c>
       <c r="N234" s="2" t="n">
-        <v>-0.1006574288856224</v>
+        <v>0.0135418981495234</v>
       </c>
       <c r="O234" s="2" t="inlineStr">
         <is>
@@ -12876,21 +12876,21 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>6160</v>
+        <v>5223</v>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>欣技</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
         <v/>
       </c>
       <c r="D235" s="2" t="n">
-        <v>89.98471763508765</v>
+        <v>90.74386851768108</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>15.75</v>
+        <v>24.55</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -12901,16 +12901,16 @@
         <v>0</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>40.4824203072439</v>
+        <v>45.06435526381252</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>13.13851783136735</v>
+        <v>15.04137883517502</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>1.030449178867092</v>
+        <v>0.0875314323301747</v>
       </c>
       <c r="K235" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L235" s="2" t="n">
         <v>0</v>
@@ -12919,7 +12919,7 @@
         <v>-1</v>
       </c>
       <c r="N235" s="2" t="n">
-        <v>-0.08615753459422031</v>
+        <v>-0.1006574288856224</v>
       </c>
       <c r="O235" s="2" t="inlineStr">
         <is>
@@ -12929,21 +12929,21 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>5465</v>
+        <v>6160</v>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>欣技</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
         <v/>
       </c>
       <c r="D236" s="2" t="n">
-        <v>89.48917338598469</v>
+        <v>89.98471763508765</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>23.6</v>
+        <v>15.75</v>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
@@ -12954,16 +12954,16 @@
         <v>0</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>32.24697717824276</v>
+        <v>40.4824203072439</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>16.13791642989717</v>
+        <v>13.13851783136735</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>0.3356790106078585</v>
+        <v>1.030449178867092</v>
       </c>
       <c r="K236" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L236" s="2" t="n">
         <v>0</v>
@@ -12972,7 +12972,7 @@
         <v>-1</v>
       </c>
       <c r="N236" s="2" t="n">
-        <v>-0.1583249294366415</v>
+        <v>-0.08615753459422031</v>
       </c>
       <c r="O236" s="2" t="inlineStr">
         <is>
@@ -12982,21 +12982,21 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>4999</v>
+        <v>5465</v>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
         <v/>
       </c>
       <c r="D237" s="2" t="n">
-        <v>87.62677142874929</v>
+        <v>89.48917338598469</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>19.75</v>
+        <v>23.6</v>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
@@ -13007,13 +13007,13 @@
         <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>41.09767456419239</v>
+        <v>32.24697717824276</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>13.73973283032402</v>
+        <v>16.13791642989717</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>0.8479897963337358</v>
+        <v>0.3356790106078585</v>
       </c>
       <c r="K237" s="2" t="n">
         <v>0</v>
@@ -13025,7 +13025,7 @@
         <v>-1</v>
       </c>
       <c r="N237" s="2" t="n">
-        <v>-0.0431032182072419</v>
+        <v>-0.1583249294366415</v>
       </c>
       <c r="O237" s="2" t="inlineStr">
         <is>
@@ -13035,52 +13035,105 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
+        <v>4999</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>鑫禾</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>87.62677142874929</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>41.09767456419239</v>
+      </c>
+      <c r="I238" s="2" t="n">
+        <v>13.73973283032402</v>
+      </c>
+      <c r="J238" s="2" t="n">
+        <v>0.8479897963337358</v>
+      </c>
+      <c r="K238" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>-0.0431032182072419</v>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
         <v>4935</v>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>茂林-KY</t>
         </is>
       </c>
-      <c r="C238" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D238" s="2" t="n">
+      <c r="C239" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D239" s="2" t="n">
         <v>60.14599941521463</v>
       </c>
-      <c r="E238" s="2" t="n">
+      <c r="E239" s="2" t="n">
         <v>36.15</v>
       </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H238" s="2" t="n">
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H239" s="2" t="n">
         <v>43.26412772134</v>
       </c>
-      <c r="I238" s="2" t="n">
+      <c r="I239" s="2" t="n">
         <v>15.92527733059761</v>
       </c>
-      <c r="J238" s="2" t="n">
+      <c r="J239" s="2" t="n">
         <v>0.4508726918648172</v>
       </c>
-      <c r="K238" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L238" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M238" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N238" s="2" t="n">
+      <c r="K239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N239" s="2" t="n">
         <v>-0.0935729949643512</v>
       </c>
-      <c r="O238" s="2" t="inlineStr">
+      <c r="O239" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
